--- a/01_Reporting_Suite/K2 DAILY REPORTING/02 EMAIL CONTROL/Email Control Register.xlsx
+++ b/01_Reporting_Suite/K2 DAILY REPORTING/02 EMAIL CONTROL/Email Control Register.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -545,8 +545,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>0</v>
       </c>
@@ -616,7 +614,6 @@
           <t>2026-07-28 14:09</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +670,6 @@
           <t>2026-07-28 14:09</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -730,7 +726,6 @@
           <t>2026-07-28 14:09</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -769,8 +764,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>0</v>
       </c>
@@ -840,7 +833,6 @@
           <t>2026-07-28 14:09</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -879,8 +871,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
         <v>0</v>
       </c>
@@ -932,8 +922,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
         <v>0</v>
       </c>
@@ -985,8 +973,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>0</v>
       </c>
@@ -1056,7 +1042,6 @@
           <t>2026-07-28 14:09</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1113,7 +1098,6 @@
           <t>2026-07-28 14:09</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1170,7 +1154,1022 @@
           <t>2026-07-28 14:09</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cleanaway</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Not Generated</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>14</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>jayden.andrew@cleanaway.com.au</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:55</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Cleanaway holds nothing on hire today - no report to send. The folder and this record are made so the day is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DGH Engineering</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ross.gould@dgh.com.au; jadams@dgh.com.au; aburgun@dgh.com.au; btooma@dgh.com.au</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:55</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 29 Jul 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Daily Safety &amp; Compliance PDF attached (0 attachment(s)) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DKE Group</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>14</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>louis.miller@dkegroup.com.au; illy.reitsma@dkegroup.com.au; warren.wilson@dkegroup.com.au; tim.lalor@dkegroup.com.au</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:55</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 29 Jul 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Daily Safety &amp; Compliance PDF attached (0 attachment(s)) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>High Risk Solutions</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ca@highrisksolutions.com.au; david.nunn@highrisksolutions.com.au; jzuniga@highrisksolutions.com.au</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:55</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 29 Jul 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Daily Safety &amp; Compliance PDF attached (0 attachment(s)) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Industec</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Not Generated</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>14</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>m.clayton@industec.com.au</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:55</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Industec holds nothing on hire today - no report to send. The folder and this record are made so the day is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Programmed</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>14</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>debra.rogers@programmed.com.au</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:55</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 29 Jul 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Daily Safety &amp; Compliance PDF attached (0 attachment(s)) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Synclift</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Not Generated</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>14</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>jbeard@synclift.com.au; blynch@synclift.com.au</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:55</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Synclift holds nothing on hire today - no report to send. The folder and this record are made so the day is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tasman Rope Access</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Not Generated</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>14</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>c.sheppardkadel@tasmanropeaccess.com</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:55</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Tasman Rope Access holds nothing on hire today - no report to send. The folder and this record are made so the day is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Universal Cranes</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Not Generated</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>14</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>joshua.breslin@universalcranes.com</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:55</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Universal Cranes holds nothing on hire today - no report to send. The folder and this record are made so the day is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Veolia Refractory</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>14</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>melissa.rowlands1@veolia.com; andrew.macloughlin@veolia.com; tim.lang1@veolia.com</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:55</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 29 Jul 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Daily Safety &amp; Compliance PDF attached (0 attachment(s)) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Xtreme Engineering</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>14</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>kkay@xtremeengineering.com.au; scotth@xtremeengineering.com.au</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:55</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 29 Jul 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Daily Safety &amp; Compliance PDF attached (0 attachment(s)) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cement Australia</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Client master report</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" t="n">
+        <v>14</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>david.moore@cemaust.com.au; benjamin.vandenbroek@cemaust.com.au; john.pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>grant.holdsworth@cemaust.com.au; hazel.barba@cemaust.com.au; carmen.groat@cemaust.com.au; daniel.osborne@cemaust.com.au; aaron.watts@cemaust.com.au; thomas.maher@coates.com.au; cody.mitchell@coates.com.au; adam.mcinnes@cemaust.com.au; kris.tierney@cemaust.com.au; melissa.cooper@cemaust.com.au; nicole.ward@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Cement Australia On-Hire Report - 2026-07-29.pdf</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:55</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 29 Jul 2026 | Daily Cost Tracking Report has no PDF - it was not built for 29 Jul 2026 | Site Plant Report has no PDF - it was not built for 29 Jul 2026 | Consumables Usage Report has no PDF - it was not built for 29 Jul 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | All five Cement attachments present (missing: Daily Safety &amp; Compliance Report, Daily Cost Tracking Report, Site Plant Report, Consumables Usage Report)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DGH Engineering</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>14</v>
+      </c>
+      <c r="F26" t="n">
+        <v>14</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ross.gould@dgh.com.au; jadams@dgh.com.au; aburgun@dgh.com.au; btooma@dgh.com.au</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>DGH Engineering - On-Hire Report - 2026-07-29.html</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>DGH Engineering - On-Hire Report - 2026-07-29.pdf; Daily Safety &amp; Compliance Report - 2026-07-29.pdf</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:15</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DKE Group</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>14</v>
+      </c>
+      <c r="F27" t="n">
+        <v>14</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>louis.miller@dkegroup.com.au; illy.reitsma@dkegroup.com.au; warren.wilson@dkegroup.com.au; tim.lalor@dkegroup.com.au</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>DKE Group - On-Hire Report - 2026-07-29.html</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>DKE Group - On-Hire Report - 2026-07-29.pdf; Daily Safety &amp; Compliance Report - 2026-07-29.pdf</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:15</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>High Risk Solutions</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>14</v>
+      </c>
+      <c r="F28" t="n">
+        <v>14</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ca@highrisksolutions.com.au; david.nunn@highrisksolutions.com.au; jzuniga@highrisksolutions.com.au</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>High Risk Solutions - On-Hire Report - 2026-07-29.html</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>High Risk Solutions - On-Hire Report - 2026-07-29.pdf; Daily Safety &amp; Compliance Report - 2026-07-29.pdf</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:15</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Programmed</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>14</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>debra.rogers@programmed.com.au</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Programmed - On-Hire Report - 2026-07-29.html</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Programmed - On-Hire Report - 2026-07-29.pdf; Daily Safety &amp; Compliance Report - 2026-07-29.pdf</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:15</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Veolia Refractory</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>14</v>
+      </c>
+      <c r="F30" t="n">
+        <v>14</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>melissa.rowlands1@veolia.com; andrew.macloughlin@veolia.com; tim.lang1@veolia.com</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Veolia Refractory - On-Hire Report - 2026-07-29.html</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Veolia Refractory - On-Hire Report - 2026-07-29.pdf; Daily Safety &amp; Compliance Report - 2026-07-29.pdf</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:15</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Xtreme Engineering</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>14</v>
+      </c>
+      <c r="F31" t="n">
+        <v>14</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>kkay@xtremeengineering.com.au; scotth@xtremeengineering.com.au</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Xtreme Engineering - On-Hire Report - 2026-07-29.html</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Xtreme Engineering - On-Hire Report - 2026-07-29.pdf; Daily Safety &amp; Compliance Report - 2026-07-29.pdf</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:15</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cement Australia</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Client master report</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>14</v>
+      </c>
+      <c r="F32" t="n">
+        <v>14</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>david.moore@cemaust.com.au; benjamin.vandenbroek@cemaust.com.au; john.pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>grant.holdsworth@cemaust.com.au; hazel.barba@cemaust.com.au; carmen.groat@cemaust.com.au; daniel.osborne@cemaust.com.au; aaron.watts@cemaust.com.au; thomas.maher@coates.com.au; cody.mitchell@coates.com.au; adam.mcinnes@cemaust.com.au; kris.tierney@cemaust.com.au; melissa.cooper@cemaust.com.au; nicole.ward@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Executive Daily Summary - 2026-07-29.html</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Executive Daily Summary - 2026-07-29.pdf; Daily Safety &amp; Compliance Report - 2026-07-29.pdf; Daily Cost Tracking Report - 2026-07-29.pdf; Site Plant Report - 2026-07-29.pdf; Cement Australia On-Hire Report - 2026-07-29 (2).pdf; Consumables Usage Report - 2026-07-29.pdf</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:15</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/01_Reporting_Suite/K2 DAILY REPORTING/02 EMAIL CONTROL/Email Control Register.xlsx
+++ b/01_Reporting_Suite/K2 DAILY REPORTING/02 EMAIL CONTROL/Email Control Register.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1827,7 +1827,6 @@
           <t>2026-07-29 14:15</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1884,7 +1883,6 @@
           <t>2026-07-29 14:15</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1941,7 +1939,6 @@
           <t>2026-07-29 14:15</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1998,7 +1995,6 @@
           <t>2026-07-29 14:15</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2055,7 +2051,6 @@
           <t>2026-07-29 14:15</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2112,7 +2107,6 @@
           <t>2026-07-29 14:15</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2169,7 +2163,642 @@
           <t>2026-07-29 14:15</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cleanaway</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Not Generated</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>9</v>
+      </c>
+      <c r="F33" t="n">
+        <v>14</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>jayden.andrew@cleanaway.com.au</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:24</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Cleanaway holds nothing on hire today - no report to send. The folder and this record are made so the day is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>DGH Engineering</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" t="n">
+        <v>14</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ross.gould@dgh.com.au; jadams@dgh.com.au; aburgun@dgh.com.au; btooma@dgh.com.au</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:24</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 03 Aug 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Daily Safety &amp; Compliance PDF attached (0 attachment(s)) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DKE Group</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" t="n">
+        <v>14</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>louis.miller@dkegroup.com.au; illy.reitsma@dkegroup.com.au; warren.wilson@dkegroup.com.au; tim.lalor@dkegroup.com.au</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:24</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 03 Aug 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Daily Safety &amp; Compliance PDF attached (0 attachment(s)) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>High Risk Solutions</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" t="n">
+        <v>14</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ca@highrisksolutions.com.au; david.nunn@highrisksolutions.com.au; jzuniga@highrisksolutions.com.au</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:24</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 03 Aug 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Daily Safety &amp; Compliance PDF attached (0 attachment(s)) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Industec</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Not Generated</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>9</v>
+      </c>
+      <c r="F37" t="n">
+        <v>14</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>m.clayton@industec.com.au</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:24</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Industec holds nothing on hire today - no report to send. The folder and this record are made so the day is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Programmed</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>10</v>
+      </c>
+      <c r="F38" t="n">
+        <v>14</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>debra.rogers@programmed.com.au</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:24</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 03 Aug 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Daily Safety &amp; Compliance PDF attached (0 attachment(s)) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Synclift</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Not Generated</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>9</v>
+      </c>
+      <c r="F39" t="n">
+        <v>14</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>jbeard@synclift.com.au; blynch@synclift.com.au</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:24</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Synclift holds nothing on hire today - no report to send. The folder and this record are made so the day is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tasman Rope Access</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Not Generated</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>c.sheppardkadel@tasmanropeaccess.com</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:24</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Tasman Rope Access holds nothing on hire today - no report to send. The folder and this record are made so the day is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Universal Cranes</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Not Generated</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>9</v>
+      </c>
+      <c r="F41" t="n">
+        <v>14</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>joshua.breslin@universalcranes.com</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:24</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Universal Cranes holds nothing on hire today - no report to send. The folder and this record are made so the day is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Veolia Refractory</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>10</v>
+      </c>
+      <c r="F42" t="n">
+        <v>14</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>melissa.rowlands1@veolia.com; andrew.macloughlin@veolia.com; tim.lang1@veolia.com</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:24</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 03 Aug 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Daily Safety &amp; Compliance PDF attached (0 attachment(s)) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Xtreme Engineering</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F43" t="n">
+        <v>14</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>kkay@xtremeengineering.com.au; scotth@xtremeengineering.com.au</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:24</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 03 Aug 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Daily Safety &amp; Compliance PDF attached (0 attachment(s)) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cement Australia</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Client master report</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>11</v>
+      </c>
+      <c r="F44" t="n">
+        <v>14</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>david.moore@cemaust.com.au; benjamin.vandenbroek@cemaust.com.au; john.pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>grant.holdsworth@cemaust.com.au; hazel.barba@cemaust.com.au; carmen.groat@cemaust.com.au; daniel.osborne@cemaust.com.au; aaron.watts@cemaust.com.au; thomas.maher@coates.com.au; cody.mitchell@coates.com.au; adam.mcinnes@cemaust.com.au; kris.tierney@cemaust.com.au; melissa.cooper@cemaust.com.au; nicole.ward@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-08-03 11:24</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 03 Aug 2026 | Daily Cost Tracking Report has no PDF - it was not built for 03 Aug 2026 | Site Plant Report has no PDF - it was not built for 03 Aug 2026 | Cement Australia On-Hire Report has no PDF - it was not built for 03 Aug 2026 | Consumables Usage Report has no PDF - it was not built for 03 Aug 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | All five Cement attachments present (missing: Daily Safety &amp; Compliance Report, Daily Cost Tracking Report, Site Plant Report, Cement Australia On-Hire Report, Consumables Usage Report)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/01_Reporting_Suite/K2 DAILY REPORTING/02 EMAIL CONTROL/Email Control Register.xlsx
+++ b/01_Reporting_Suite/K2 DAILY REPORTING/02 EMAIL CONTROL/Email Control Register.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2201,8 +2201,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
         <v>0</v>
       </c>
@@ -2254,8 +2252,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="n">
         <v>0</v>
       </c>
@@ -2307,8 +2303,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
         <v>0</v>
       </c>
@@ -2360,8 +2354,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
         <v>0</v>
       </c>
@@ -2413,8 +2405,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
         <v>0</v>
       </c>
@@ -2466,8 +2456,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
         <v>0</v>
       </c>
@@ -2519,8 +2507,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="n">
         <v>0</v>
       </c>
@@ -2572,8 +2558,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
         <v>0</v>
       </c>
@@ -2625,8 +2609,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
         <v>0</v>
       </c>
@@ -2678,8 +2660,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
         <v>0</v>
       </c>
@@ -2731,8 +2711,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
         <v>0</v>
       </c>
@@ -2784,8 +2762,6 @@
           <t>grant.holdsworth@cemaust.com.au; hazel.barba@cemaust.com.au; carmen.groat@cemaust.com.au; daniel.osborne@cemaust.com.au; aaron.watts@cemaust.com.au; thomas.maher@coates.com.au; cody.mitchell@coates.com.au; adam.mcinnes@cemaust.com.au; kris.tierney@cemaust.com.au; melissa.cooper@cemaust.com.au; nicole.ward@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="n">
         <v>0</v>
       </c>
@@ -2799,6 +2775,623 @@
           <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 03 Aug 2026 | Daily Cost Tracking Report has no PDF - it was not built for 03 Aug 2026 | Site Plant Report has no PDF - it was not built for 03 Aug 2026 | Cement Australia On-Hire Report has no PDF - it was not built for 03 Aug 2026 | Consumables Usage Report has no PDF - it was not built for 03 Aug 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | All five Cement attachments present (missing: Daily Safety &amp; Compliance Report, Daily Cost Tracking Report, Site Plant Report, Cement Australia On-Hire Report, Consumables Usage Report)</t>
         </is>
       </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>DGH Engineering</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>14</v>
+      </c>
+      <c r="F45" t="n">
+        <v>14</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ross.gould@dgh.com.au; jadams@dgh.com.au; aburgun@dgh.com.au; btooma@dgh.com.au</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>DGH Engineering - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>DGH Engineering - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>DKE Group</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>14</v>
+      </c>
+      <c r="F46" t="n">
+        <v>14</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>louis.miller@dkegroup.com.au; illy.reitsma@dkegroup.com.au; warren.wilson@dkegroup.com.au; tim.lalor@dkegroup.com.au</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>DKE Group - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>DKE Group - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>High Risk Solutions</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>14</v>
+      </c>
+      <c r="F47" t="n">
+        <v>14</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ca@highrisksolutions.com.au; david.nunn@highrisksolutions.com.au; jzuniga@highrisksolutions.com.au</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>High Risk Solutions - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>High Risk Solutions - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Programmed</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>14</v>
+      </c>
+      <c r="F48" t="n">
+        <v>14</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>debra.rogers@programmed.com.au</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Programmed - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Programmed - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Veolia Refractory</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>14</v>
+      </c>
+      <c r="F49" t="n">
+        <v>14</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>melissa.rowlands1@veolia.com; andrew.macloughlin@veolia.com; tim.lang1@veolia.com</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Veolia Refractory - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Veolia Refractory - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Xtreme Engineering</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>14</v>
+      </c>
+      <c r="F50" t="n">
+        <v>14</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>kkay@xtremeengineering.com.au; scotth@xtremeengineering.com.au</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Xtreme Engineering - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Xtreme Engineering - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Industec</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>14</v>
+      </c>
+      <c r="F51" t="n">
+        <v>14</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>m.clayton@industec.com.au</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Industec - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Industec - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Synclift</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>14</v>
+      </c>
+      <c r="F52" t="n">
+        <v>14</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>jbeard@synclift.com.au; blynch@synclift.com.au</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Synclift - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Synclift - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tasman Rope Access</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>14</v>
+      </c>
+      <c r="F53" t="n">
+        <v>14</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>c.sheppardkadel@tasmanropeaccess.com</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Tasman Rope Access - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Tasman Rope Access - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Universal Cranes</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>14</v>
+      </c>
+      <c r="F54" t="n">
+        <v>14</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>joshua.breslin@universalcranes.com</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Universal Cranes - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Universal Cranes - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Cement Australia</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Client master report</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>14</v>
+      </c>
+      <c r="F55" t="n">
+        <v>14</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>david.moore@cemaust.com.au; benjamin.vandenbroek@cemaust.com.au; john.pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>grant.holdsworth@cemaust.com.au; hazel.barba@cemaust.com.au; carmen.groat@cemaust.com.au; daniel.osborne@cemaust.com.au; aaron.watts@cemaust.com.au; thomas.maher@coates.com.au; cody.mitchell@coates.com.au; adam.mcinnes@cemaust.com.au; kris.tierney@cemaust.com.au; melissa.cooper@cemaust.com.au; nicole.ward@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Executive Daily Summary - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Executive Daily Summary - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf; Daily Cost Tracking Report - 2026-08-03 (2).pdf; Site Plant Report - 2026-08-03.pdf; Cement Australia On-Hire Report - 2026-08-03 (3).pdf; Consumables Usage Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:30</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/01_Reporting_Suite/K2 DAILY REPORTING/02 EMAIL CONTROL/Email Control Register.xlsx
+++ b/01_Reporting_Suite/K2 DAILY REPORTING/02 EMAIL CONTROL/Email Control Register.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3391,7 +3391,416 @@
           <t>2026-08-03 12:30</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Bosch Rexroth</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>13</v>
+      </c>
+      <c r="F56" t="n">
+        <v>14</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>gerhardus.vanderwesthuizen@boschrexroth.com.au</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Bosch Rexroth - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Bosch Rexroth - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-08-03 19:07</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Every address on the contact register for this company (not on the register: gerhardus.vanderwesthuizen@boschrexroth.com.au)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Industrial Rescue</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>12</v>
+      </c>
+      <c r="F57" t="n">
+        <v>14</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>chris.short@iretcq.com</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Industrial Rescue - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Industrial Rescue - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-08-03 19:07</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No other company's information in the pack (found: (this report does not name Industrial Rescue &amp; Emergency Training)) | Every address on the contact register for this company (not on the register: chris.short@iretcq.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Filtercare</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>13</v>
+      </c>
+      <c r="F58" t="n">
+        <v>14</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>admin@industec.com.au</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Filtercare - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Filtercare - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-08-03 19:07</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Every address on the contact register for this company (not on the register: admin@industec.com.au)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>QWest Crane Hire</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>13</v>
+      </c>
+      <c r="F59" t="n">
+        <v>14</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>QWest Crane Hire - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>QWest Crane Hire - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-08-03 19:07</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>At least one confirmed address in To (0 in To)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Bosch Rexroth</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>14</v>
+      </c>
+      <c r="F60" t="n">
+        <v>14</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>gerhardus.vanderwesthuizen@boschrexroth.com.au</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Bosch Rexroth - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Bosch Rexroth - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-08-03 19:08</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Industrial Rescue</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>14</v>
+      </c>
+      <c r="F61" t="n">
+        <v>14</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>chris.short@iretcq.com</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Industrial Rescue - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Industrial Rescue - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-08-03 19:08</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Filtercare</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>14</v>
+      </c>
+      <c r="F62" t="n">
+        <v>14</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>admin@industec.com.au</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Filtercare - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Filtercare - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-08-03 19:08</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/01_Reporting_Suite/K2 DAILY REPORTING/02 EMAIL CONTROL/Email Control Register.xlsx
+++ b/01_Reporting_Suite/K2 DAILY REPORTING/02 EMAIL CONTROL/Email Control Register.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3686,7 +3686,6 @@
           <t>2026-08-03 19:08</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3743,7 +3742,6 @@
           <t>2026-08-03 19:08</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3800,7 +3798,120 @@
           <t>2026-08-03 19:08</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Aestec</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>14</v>
+      </c>
+      <c r="F63" t="n">
+        <v>14</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>accounts@aestec.com.au</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Aestec - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Aestec - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-08-03 19:23</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cutrite</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>14</v>
+      </c>
+      <c r="F64" t="n">
+        <v>14</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>matt@cutrite.net.au</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Cutrite - On-Hire Report - 2026-08-03.html</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Cutrite - On-Hire Report - 2026-08-03.pdf; Daily Safety &amp; Compliance Report - 2026-08-03.pdf</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-08-03 19:23</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/01_Reporting_Suite/K2 DAILY REPORTING/02 EMAIL CONTROL/Email Control Register.xlsx
+++ b/01_Reporting_Suite/K2 DAILY REPORTING/02 EMAIL CONTROL/Email Control Register.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3854,7 +3854,6 @@
           <t>2026-08-03 19:23</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3911,7 +3910,956 @@
           <t>2026-08-03 19:23</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Cleanaway</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Not Generated</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>9</v>
+      </c>
+      <c r="F65" t="n">
+        <v>14</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>jayden.andrew@cleanaway.com.au</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Cleanaway holds nothing on hire today - no report to send. The folder and this record are made so the day is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>DGH Engineering</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>10</v>
+      </c>
+      <c r="F66" t="n">
+        <v>14</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ross.gould@dgh.com.au; jadams@dgh.com.au; aburgun@dgh.com.au; btooma@dgh.com.au</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>DKE Group</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>10</v>
+      </c>
+      <c r="F67" t="n">
+        <v>14</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>louis.miller@dkegroup.com.au; illy.reitsma@dkegroup.com.au; warren.wilson@dkegroup.com.au; tim.lalor@dkegroup.com.au</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>High Risk Solutions</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>10</v>
+      </c>
+      <c r="F68" t="n">
+        <v>14</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ca@highrisksolutions.com.au; david.nunn@highrisksolutions.com.au; jzuniga@highrisksolutions.com.au</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Industec</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>10</v>
+      </c>
+      <c r="F69" t="n">
+        <v>14</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>m.clayton@industec.com.au</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Programmed</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>10</v>
+      </c>
+      <c r="F70" t="n">
+        <v>14</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>debra.rogers@programmed.com.au</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Synclift</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>10</v>
+      </c>
+      <c r="F71" t="n">
+        <v>14</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>jbeard@synclift.com.au; blynch@synclift.com.au</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tasman Rope Access</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>10</v>
+      </c>
+      <c r="F72" t="n">
+        <v>14</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>c.sheppardkadel@tasmanropeaccess.com</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Universal Cranes</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>10</v>
+      </c>
+      <c r="F73" t="n">
+        <v>14</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>joshua.breslin@universalcranes.com</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Veolia Refractory</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>10</v>
+      </c>
+      <c r="F74" t="n">
+        <v>14</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>melissa.rowlands1@veolia.com; andrew.macloughlin@veolia.com; tim.lang1@veolia.com</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Xtreme Engineering</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>kkay@xtremeengineering.com.au; scotth@xtremeengineering.com.au</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Cement Australia</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Client master report</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>11</v>
+      </c>
+      <c r="F76" t="n">
+        <v>14</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>david.moore@cemaust.com.au; benjamin.vandenbroek@cemaust.com.au; john.pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>grant.holdsworth@cemaust.com.au; hazel.barba@cemaust.com.au; carmen.groat@cemaust.com.au; daniel.osborne@cemaust.com.au; aaron.watts@cemaust.com.au; thomas.maher@coates.com.au; cody.mitchell@coates.com.au; adam.mcinnes@cemaust.com.au; kris.tierney@cemaust.com.au; melissa.cooper@cemaust.com.au; nicole.ward@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 04 Aug 2026 | Daily Cost Tracking Report has no PDF - it was not built for 04 Aug 2026 | Site Plant Report has no PDF - it was not built for 04 Aug 2026 | Cement Australia On-Hire Report has no PDF - it was not built for 04 Aug 2026 | Consumables Usage Report has no PDF - it was not built for 04 Aug 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | All five Cement attachments present (missing: Daily Safety &amp; Compliance Report, Daily Cost Tracking Report, Site Plant Report, Cement Australia On-Hire Report, Consumables Usage Report)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Bosch Rexroth</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>10</v>
+      </c>
+      <c r="F77" t="n">
+        <v>14</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>gerhardus.vanderwesthuizen@boschrexroth.com.au</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Industrial Rescue</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>10</v>
+      </c>
+      <c r="F78" t="n">
+        <v>14</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>chris.short@iretcq.com</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Filtercare</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>10</v>
+      </c>
+      <c r="F79" t="n">
+        <v>14</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>admin@industec.com.au</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>QWest Crane Hire</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>9</v>
+      </c>
+      <c r="F80" t="n">
+        <v>14</v>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>At least one confirmed address in To (0 in To) | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Aestec</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>10</v>
+      </c>
+      <c r="F81" t="n">
+        <v>14</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>accounts@aestec.com.au</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Cutrite</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>10</v>
+      </c>
+      <c r="F82" t="n">
+        <v>14</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>matt@cutrite.net.au</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-08-04 01:06</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/01_Reporting_Suite/K2 DAILY REPORTING/02 EMAIL CONTROL/Email Control Register.xlsx
+++ b/01_Reporting_Suite/K2 DAILY REPORTING/02 EMAIL CONTROL/Email Control Register.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3948,8 +3948,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="n">
         <v>0</v>
       </c>
@@ -4001,8 +3999,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="n">
         <v>0</v>
       </c>
@@ -4054,8 +4050,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="n">
         <v>0</v>
       </c>
@@ -4107,8 +4101,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="n">
         <v>0</v>
       </c>
@@ -4160,8 +4152,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="n">
         <v>0</v>
       </c>
@@ -4213,8 +4203,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="n">
         <v>0</v>
       </c>
@@ -4266,8 +4254,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="n">
         <v>0</v>
       </c>
@@ -4319,8 +4305,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
         <v>0</v>
       </c>
@@ -4372,8 +4356,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="n">
         <v>0</v>
       </c>
@@ -4425,8 +4407,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
         <v>0</v>
       </c>
@@ -4478,8 +4458,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="n">
         <v>0</v>
       </c>
@@ -4531,8 +4509,6 @@
           <t>grant.holdsworth@cemaust.com.au; hazel.barba@cemaust.com.au; carmen.groat@cemaust.com.au; daniel.osborne@cemaust.com.au; aaron.watts@cemaust.com.au; thomas.maher@coates.com.au; cody.mitchell@coates.com.au; adam.mcinnes@cemaust.com.au; kris.tierney@cemaust.com.au; melissa.cooper@cemaust.com.au; nicole.ward@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="n">
         <v>0</v>
       </c>
@@ -4584,8 +4560,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="n">
         <v>0</v>
       </c>
@@ -4637,8 +4611,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="n">
         <v>0</v>
       </c>
@@ -4690,8 +4662,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="n">
         <v>0</v>
       </c>
@@ -4733,14 +4703,11 @@
       <c r="F80" t="n">
         <v>14</v>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="n">
         <v>0</v>
       </c>
@@ -4792,8 +4759,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="n">
         <v>0</v>
       </c>
@@ -4845,8 +4810,6 @@
           <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="n">
         <v>0</v>
       </c>
@@ -4860,6 +4823,971 @@
           <t>Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | Their own report is the only attachment (nothing attached) | No other company's information in the pack (found: (there is no report to read))</t>
         </is>
       </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Cleanaway</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Not Generated</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>9</v>
+      </c>
+      <c r="F83" t="n">
+        <v>14</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>jayden.andrew@cleanaway.com.au</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Cleanaway holds nothing on hire today - no report to send. The folder and this record are made so the day is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>DGH Engineering</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>14</v>
+      </c>
+      <c r="F84" t="n">
+        <v>14</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ross.gould@dgh.com.au; jadams@dgh.com.au; aburgun@dgh.com.au; btooma@dgh.com.au</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>DGH Engineering - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>DGH Engineering - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>DKE Group</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>14</v>
+      </c>
+      <c r="F85" t="n">
+        <v>14</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>louis.miller@dkegroup.com.au; illy.reitsma@dkegroup.com.au; warren.wilson@dkegroup.com.au; tim.lalor@dkegroup.com.au</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>DKE Group - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>DKE Group - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>High Risk Solutions</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>14</v>
+      </c>
+      <c r="F86" t="n">
+        <v>14</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ca@highrisksolutions.com.au; david.nunn@highrisksolutions.com.au; jzuniga@highrisksolutions.com.au</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>High Risk Solutions - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>High Risk Solutions - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Industec</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>14</v>
+      </c>
+      <c r="F87" t="n">
+        <v>14</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>m.clayton@industec.com.au</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Industec - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Industec - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Programmed</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>14</v>
+      </c>
+      <c r="F88" t="n">
+        <v>14</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>debra.rogers@programmed.com.au</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Programmed - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Programmed - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Synclift</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>14</v>
+      </c>
+      <c r="F89" t="n">
+        <v>14</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>jbeard@synclift.com.au; blynch@synclift.com.au</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Synclift - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Synclift - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tasman Rope Access</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>14</v>
+      </c>
+      <c r="F90" t="n">
+        <v>14</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>c.sheppardkadel@tasmanropeaccess.com</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Tasman Rope Access - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Tasman Rope Access - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Universal Cranes</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>14</v>
+      </c>
+      <c r="F91" t="n">
+        <v>14</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>joshua.breslin@universalcranes.com</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Universal Cranes - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Universal Cranes - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Veolia Refractory</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>14</v>
+      </c>
+      <c r="F92" t="n">
+        <v>14</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>melissa.rowlands1@veolia.com; andrew.macloughlin@veolia.com; tim.lang1@veolia.com</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Veolia Refractory - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Veolia Refractory - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Xtreme Engineering</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>14</v>
+      </c>
+      <c r="F93" t="n">
+        <v>14</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>kkay@xtremeengineering.com.au; scotth@xtremeengineering.com.au</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Xtreme Engineering - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Xtreme Engineering - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Cement Australia</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Client master report</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Failed - Review Required</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>11</v>
+      </c>
+      <c r="F94" t="n">
+        <v>14</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>david.moore@cemaust.com.au; benjamin.vandenbroek@cemaust.com.au; john.pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>grant.holdsworth@cemaust.com.au; hazel.barba@cemaust.com.au; carmen.groat@cemaust.com.au; daniel.osborne@cemaust.com.au; aaron.watts@cemaust.com.au; thomas.maher@coates.com.au; cody.mitchell@coates.com.au; adam.mcinnes@cemaust.com.au; kris.tierney@cemaust.com.au; melissa.cooper@cemaust.com.au; nicole.ward@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Cement Australia On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Daily Safety &amp; Compliance Report has no PDF - it was not built for 05 Aug 2026 | Daily Cost Tracking Report has no PDF - it was not built for 05 Aug 2026 | Site Plant Report has no PDF - it was not built for 05 Aug 2026 | Consumables Usage Report has no PDF - it was not built for 05 Aug 2026 | Report in the body is today's, and still the current one (nothing generated) | Report ready for the email body (nothing generated) | All five Cement attachments present (missing: Daily Safety &amp; Compliance Report, Daily Cost Tracking Report, Site Plant Report, Consumables Usage Report)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Bosch Rexroth</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>14</v>
+      </c>
+      <c r="F95" t="n">
+        <v>14</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>gerhardus.vanderwesthuizen@boschrexroth.com.au</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Bosch Rexroth - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Bosch Rexroth - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Industrial Rescue</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>14</v>
+      </c>
+      <c r="F96" t="n">
+        <v>14</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>chris.short@iretcq.com</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Industrial Rescue - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Industrial Rescue - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Filtercare</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>14</v>
+      </c>
+      <c r="F97" t="n">
+        <v>14</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>admin@industec.com.au</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Filtercare - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Filtercare - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Aestec</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>14</v>
+      </c>
+      <c r="F98" t="n">
+        <v>14</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>accounts@aestec.com.au</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Aestec - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Aestec - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Cutrite</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>External contractor</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Draft Ready</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>14</v>
+      </c>
+      <c r="F99" t="n">
+        <v>14</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>matt@cutrite.net.au</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>thomas.maher@coates.com.au; cody.mitchell@coates.com.au; benjamin.vandenbroek@cemaust.com.au; david.moore@cemaust.com.au; John.Pickels@cemaust.com.au</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Cutrite - On-Hire Report - 2026-08-05.html</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Cutrite - On-Hire Report - 2026-08-05.pdf</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:25</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
